--- a/06-content-engine/templates/content-workbook.xlsx
+++ b/06-content-engine/templates/content-workbook.xlsx
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -733,6 +734,11 @@
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Ảnh Drive</t>
         </is>
       </c>
     </row>
@@ -843,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -853,6 +859,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,6 +898,11 @@
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Ảnh Drive</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/06-content-engine/templates/content-workbook.xlsx
+++ b/06-content-engine/templates/content-workbook.xlsx
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,6 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,11 +733,6 @@
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Ghi chú</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Ảnh Drive</t>
         </is>
       </c>
     </row>
@@ -849,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -859,7 +853,6 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,11 +891,6 @@
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Ảnh Drive</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
